--- a/飞鸽批量导入新增自定义知识模版.xlsx
+++ b/飞鸽批量导入新增自定义知识模版.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" tabRatio="500" activeTab="1"/>
+    <workbookView windowHeight="15600" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="上传模板" sheetId="1" r:id="rId1"/>
     <sheet name="模板示例说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>知识编号</t>
   </si>
@@ -32,7 +45,10 @@
     <t>图片答案</t>
   </si>
   <si>
-    <t>绑定商品</t>
+    <t>绑定商品ID/系统类目</t>
+  </si>
+  <si>
+    <t>绑定商品自定义类目</t>
   </si>
   <si>
     <t>关联订单状态</t>
@@ -188,7 +204,7 @@
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">1、请填写“全部商品”，或多个“具体的商品分类中文名称”（多个分类之间用alt+回车符号分割），或多个“商品id”（多个id之间用alt+回车符号分割）。只能同时填写一类。
+      <t xml:space="preserve">1、请填写“全部商品”，或多个“具体的系统商品类目中文名称”（多个分类之间用alt+回车符号分割），或多个“商品id”（多个id之间用alt+回车符号分割）。只能同时填写其中一类。
 </t>
     </r>
     <r>
@@ -199,13 +215,68 @@
         <charset val="134"/>
       </rPr>
       <t>2、多级分类需用“-”区隔每一级分类，如“男鞋-皮鞋-牛津鞋”。
-3、若未填写，默认为“全部商品”。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">如果一个答案，同时关联多个商品，请在同一条记录里填写。
+3、若商品ID/系统类目和商品自定义类目都未填写，默认为“全部商品”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、如同一条记录中同时填写商品ID/系统类目和商品自定义类目，则以商品自定义类目为准，忽略商品ID/系统类目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">如果一个答案，同时关联多个商品/类目，请在同一条记录里填写。
 如果您把同一个答案分成多行、每行写一个商品id，可能会导致系统创建多个相同答案，导致后期维护成本变高
 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">1、请填写一个或多个“具体的商品自定义分类中文名称”（多个分类之间用alt+回车符号分割）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、多级分类需用“-”区隔每一级分类，如“男鞋-皮鞋-牛津鞋”。
+3、若商品ID/系统类目和商品自定义类目都未填写，默认为“全部商品”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4、如同一条记录中同时填写商品ID/系统类目和商品自定义类目，则以商品自定义类目为准，忽略商品ID/系统类目</t>
+    </r>
+  </si>
+  <si>
+    <t>如果一个答案，同时关联多个类目，请在同一条记录里填写。
+如果您把同一个答案分成多行、每行写一个商品id，可能会导致系统创建多个相同答案，导致后期维护成本变高</t>
   </si>
   <si>
     <r>
@@ -363,14 +434,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -422,17 +493,70 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -445,7 +569,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -460,77 +615,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -543,26 +628,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -606,19 +682,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -630,145 +844,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,11 +899,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -841,13 +932,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -882,40 +977,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -923,174 +999,174 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="17" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="24" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="19" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="19" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="19" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="22" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1099,11 +1175,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="19" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="19" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="22" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1115,7 +1197,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1130,54 +1212,54 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
@@ -1510,87 +1592,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="10.8303571428571" defaultRowHeight="17.6" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="17" customWidth="1"/>
-    <col min="2" max="2" width="16.1607142857143" style="17" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="17" customWidth="1"/>
-    <col min="4" max="4" width="19.6607142857143" style="17" customWidth="1"/>
-    <col min="5" max="8" width="16.5" style="17" customWidth="1"/>
-    <col min="9" max="9" width="16.1607142857143" style="17" customWidth="1"/>
-    <col min="10" max="10" width="23.6607142857143" style="17" customWidth="1"/>
-    <col min="11" max="11" width="16.1607142857143" style="17" customWidth="1"/>
-    <col min="12" max="12" width="18" style="17" customWidth="1"/>
-    <col min="13" max="13" width="20.8303571428571" style="17" customWidth="1"/>
-    <col min="14" max="14" width="19.1607142857143" style="17" customWidth="1"/>
-    <col min="15" max="15" width="18.6607142857143" style="17" customWidth="1"/>
-    <col min="16" max="16" width="18.1607142857143" style="17" customWidth="1"/>
-    <col min="17" max="17" width="21" style="18" customWidth="1"/>
-    <col min="18" max="16384" width="10.8303571428571" style="17"/>
+    <col min="1" max="1" width="11.5" style="19" customWidth="1"/>
+    <col min="2" max="2" width="16.1607142857143" style="19" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="19" customWidth="1"/>
+    <col min="4" max="4" width="19.6607142857143" style="19" customWidth="1"/>
+    <col min="5" max="9" width="16.5" style="19" customWidth="1"/>
+    <col min="10" max="10" width="16.1607142857143" style="19" customWidth="1"/>
+    <col min="11" max="11" width="23.6607142857143" style="19" customWidth="1"/>
+    <col min="12" max="12" width="16.1607142857143" style="19" customWidth="1"/>
+    <col min="13" max="13" width="18" style="19" customWidth="1"/>
+    <col min="14" max="14" width="20.8303571428571" style="19" customWidth="1"/>
+    <col min="15" max="15" width="19.1607142857143" style="19" customWidth="1"/>
+    <col min="16" max="16" width="18.6607142857143" style="19" customWidth="1"/>
+    <col min="17" max="17" width="18.1607142857143" style="19" customWidth="1"/>
+    <col min="18" max="18" width="21" style="20" customWidth="1"/>
+    <col min="19" max="16384" width="10.8303571428571" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="36" spans="1:18">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="21" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="23" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="15:15">
-      <c r="O2" s="22"/>
-    </row>
-    <row r="3" spans="15:15">
-      <c r="O3" s="22"/>
-    </row>
-    <row r="4" spans="15:15">
-      <c r="O4" s="22"/>
+      <c r="R1" s="25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="16:16">
+      <c r="P2" s="24"/>
+    </row>
+    <row r="3" spans="16:16">
+      <c r="P3" s="24"/>
+    </row>
+    <row r="4" spans="16:16">
+      <c r="P4" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1602,8 +1687,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="15.2" outlineLevelCol="3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="17.6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20.1607142857143" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.8303571428571" style="2" customWidth="1"/>
@@ -1612,24 +1697,24 @@
     <col min="5" max="16384" width="8.83035714285714" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:1">
+    <row r="1" ht="34.4" spans="1:1">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" ht="16" spans="1:1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="18" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="16" spans="1:1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="18" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -1637,30 +1722,30 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="61" spans="1:4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" ht="53" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="51" customHeight="1" spans="1:4">
@@ -1668,13 +1753,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:4">
@@ -1682,10 +1767,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11"/>
     </row>
@@ -1694,120 +1779,122 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="11" ht="88" customHeight="1" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" s="13"/>
     </row>
-    <row r="12" ht="68" spans="1:4">
-      <c r="A12" s="5" t="s">
+    <row r="12" s="1" customFormat="1" ht="88" spans="1:4">
+      <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>30</v>
+      <c r="B12" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="86" customHeight="1" spans="1:4">
-      <c r="A13" s="15" t="s">
+      <c r="D12" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="77" customHeight="1" spans="1:4">
+      <c r="A13" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="16"/>
-    </row>
-    <row r="14" ht="54" customHeight="1" spans="1:4">
-      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A14" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>30</v>
+      <c r="B14" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="58" customHeight="1" spans="1:4">
-      <c r="A15" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18"/>
+    </row>
+    <row r="15" ht="54" customHeight="1" spans="1:4">
+      <c r="A15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>38</v>
+      <c r="B15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="D15" s="13"/>
     </row>
-    <row r="16" customFormat="1" ht="46" spans="1:4">
+    <row r="16" s="1" customFormat="1" ht="58" customHeight="1" spans="1:4">
       <c r="A16" s="15" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" ht="46" spans="1:4">
-      <c r="A17" s="5" t="s">
+    <row r="17" customFormat="1" ht="53" spans="1:4">
+      <c r="A17" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>30</v>
+      <c r="B17" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" ht="55" customHeight="1" spans="1:4">
+    <row r="18" ht="53" spans="1:4">
       <c r="A18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="19" ht="55" customHeight="1" spans="1:4">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="D19" s="13"/>
     </row>
@@ -1815,49 +1902,61 @@
       <c r="A20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>30</v>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="15"/>
+        <v>45</v>
+      </c>
+      <c r="D20" s="13"/>
     </row>
     <row r="21" ht="55" customHeight="1" spans="1:4">
       <c r="A21" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D21" s="15"/>
     </row>
-    <row r="22" ht="57" customHeight="1" spans="1:4">
-      <c r="A22" s="5" t="s">
+    <row r="22" ht="55" customHeight="1" spans="1:4">
+      <c r="A22" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" ht="151" customHeight="1" spans="1:4">
+      <c r="B22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="15"/>
+    </row>
+    <row r="23" ht="57" customHeight="1" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>47</v>
+        <v>31</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="D23" s="5"/>
+    </row>
+    <row r="24" ht="151" customHeight="1" spans="1:4">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
